--- a/complexity_metrics.xlsx
+++ b/complexity_metrics.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="47">
   <si>
     <t>Package Name</t>
   </si>
@@ -44,94 +44,115 @@
     <t>High Weight Table List</t>
   </si>
   <si>
+    <t>High Weight Procedure Count</t>
+  </si>
+  <si>
+    <t>High Weight Procedure List</t>
+  </si>
+  <si>
     <t>Subquery Count</t>
   </si>
   <si>
+    <t>Table Count</t>
+  </si>
+  <si>
+    <t>Table List</t>
+  </si>
+  <si>
+    <t>Has Exceptions</t>
+  </si>
+  <si>
+    <t>Failed Statements</t>
+  </si>
+  <si>
     <t>complex_procedure</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>employees, jobs, salary_history, department_budgets, notifications, EMPLOYEE, DEPARTMENT</t>
+  </si>
+  <si>
     <t>complex_query</t>
   </si>
   <si>
+    <t>employees, employees, job_history</t>
+  </si>
+  <si>
     <t>window_functions</t>
   </si>
   <si>
     <t>custom_functions_procedure</t>
   </si>
   <si>
+    <t>calculate_discount, calculate_shipping_cost, calculate_loyalty_points, calculate_processing_fee</t>
+  </si>
+  <si>
+    <t>customers, shopping_cart, DUAL, orders, order_items, notifications, error_log, CUSTOMER, CART</t>
+  </si>
+  <si>
     <t>a</t>
   </si>
   <si>
     <t>delete_test</t>
   </si>
   <si>
+    <t>mid_yjqs_detail</t>
+  </si>
+  <si>
     <t>nested_loops_procedure</t>
   </si>
   <si>
+    <t>departments, employees, sales, performance_analysis_log, large_sale_analysis, employee_performance, department_performance, overall_performance, performance_alerts, error_log, DEPARTMENT, PREVIOUS</t>
+  </si>
+  <si>
     <t>nested_procedure_calls</t>
   </si>
   <si>
+    <t>calculate_commission, calculate_deductions</t>
+  </si>
+  <si>
+    <t>departments, employees, sales, sale_date, commission_log, employee_benefits, deduction_log, DUAL, payslips, payment_history, error_log, department_payrolls, company_payrolls, payroll_reports, EMPLOYEE, DEPARTMENT, COMPANY</t>
+  </si>
+  <si>
     <t>cte_query</t>
   </si>
   <si>
     <t>simple_procedure</t>
   </si>
   <si>
+    <t>EMPLOYEES</t>
+  </si>
+  <si>
     <t>delete_test2</t>
   </si>
   <si>
+    <t>MID_YJQS_DETAIL</t>
+  </si>
+  <si>
     <t>AAATEST2</t>
   </si>
   <si>
+    <t>PKG_HTTP_MNG.PRC_ADD_RECV_INST</t>
+  </si>
+  <si>
     <t>._AAATEST2</t>
   </si>
   <si>
     <t>simple_query</t>
   </si>
   <si>
+    <t>employees</t>
+  </si>
+  <si>
     <t>AAATEST1</t>
   </si>
   <si>
+    <t>PAR_ACCOUNT_CUSSENT, par_clr_acnt_info, mid_yjqs_detail, V_ALL_ACNT_INFO_BASE, P_SQL2</t>
+  </si>
+  <si>
     <t>._AAATEST1</t>
-  </si>
-  <si>
-    <t>package_body</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_appinfo</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_servinfo</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_monitor_switch</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_useablity_info</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_trade_define</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_resource_define</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_trade_info</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_resource_info</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_arm_config</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_staticsparma_valve</t>
-  </si>
-  <si>
-    <t>BIGFUND.CTP_MX_PCKG_INIT.proc_get_staticsparma_period</t>
   </si>
 </sst>
 </file>
@@ -193,20 +214,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.76953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="54.05078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.76953125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.2890625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.59765625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="11.97265625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="23.55078125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="23.34375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="21.15625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="84.98046875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="24.7109375" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="22.5234375" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="28.98828125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="34.78125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="16.2109375" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="12.578125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="209.4296875" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="15.46875" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="17.85546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -243,13 +270,31 @@
       <c r="K1" t="s" s="1">
         <v>10</v>
       </c>
+      <c r="L1" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>115.0</v>
@@ -267,30 +312,48 @@
         <v>0.0</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="O2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="P2" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>12.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>0.0</v>
@@ -302,24 +365,42 @@
         <v>0.0</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M3" t="n" s="0">
         <v>2.0</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="O3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="P3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>27.0</v>
@@ -337,30 +418,48 @@
         <v>0.0</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="P4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>292.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>71.0</v>
+        <v>47.0</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>0.0</v>
@@ -369,27 +468,45 @@
         <v>0.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="O5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="P5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>114.0</v>
@@ -407,24 +524,42 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N6" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="O6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="P6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>3.0</v>
@@ -442,30 +577,48 @@
         <v>0.0</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K7" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="P7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>335.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>107.5</v>
+        <v>120.5</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>4.0</v>
@@ -477,30 +630,48 @@
         <v>0.0</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M8" t="n" s="0">
         <v>1.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="P8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>525.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>118.5</v>
+        <v>112.5</v>
       </c>
       <c r="E9" t="n" s="0">
         <v>2.0</v>
@@ -509,27 +680,45 @@
         <v>1.0</v>
       </c>
       <c r="G9" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="P9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>59.0</v>
@@ -547,24 +736,42 @@
         <v>0.0</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="P10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>4.0</v>
@@ -582,24 +789,42 @@
         <v>0.0</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="P11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>8.0</v>
@@ -617,30 +842,48 @@
         <v>0.0</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L12" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="P12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>80.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>57.0</v>
+        <v>62.0</v>
       </c>
       <c r="E13" t="n" s="0">
         <v>0.0</v>
@@ -652,24 +895,42 @@
         <v>0.0</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J13" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="P13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>3.0</v>
@@ -687,24 +948,42 @@
         <v>0.0</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="P14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>1.0</v>
@@ -722,30 +1001,48 @@
         <v>0.0</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="L15" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="P15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>352.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>137.5</v>
+        <v>142.5</v>
       </c>
       <c r="E16" t="n" s="0">
         <v>1.0</v>
@@ -757,24 +1054,42 @@
         <v>0.0</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="L16" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="P16" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>6.0</v>
@@ -792,401 +1107,34 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J17" t="s" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K17" t="n" s="0">
         <v>0.0</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C18" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D18" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="E18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J18" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K18" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C19" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="D19" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E19" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F19" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G19" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I19" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J19" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K19" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="C20" t="n" s="0">
-        <v>9.0</v>
-      </c>
-      <c r="D20" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E20" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F20" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G20" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H20" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I20" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J20" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K20" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C21" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="D21" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E21" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F21" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G21" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H21" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I21" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J21" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K21" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C22" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="D22" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E22" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F22" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G22" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H22" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I22" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J22" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K22" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="C23" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="D23" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E23" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F23" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G23" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H23" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I23" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J23" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K23" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C24" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D24" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E24" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F24" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G24" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H24" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I24" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J24" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K24" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="C25" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D25" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E25" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F25" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G25" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H25" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I25" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J25" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K25" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="C26" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="D26" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E26" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F26" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G26" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H26" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I26" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J26" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K26" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C27" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="D27" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="E27" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F27" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G27" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H27" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I27" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J27" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K27" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="C28" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="D28" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="E28" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="F28" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="G28" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H28" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="I28" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J28" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="K28" t="n" s="0">
-        <v>0.0</v>
+      <c r="L17" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="P17" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s" s="0">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/complexity_metrics.xlsx
+++ b/complexity_metrics.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="103">
   <si>
     <t>Package Name</t>
   </si>
@@ -80,13 +80,31 @@
     <t>Procedure Call Details</t>
   </si>
   <si>
+    <t>Hint Count</t>
+  </si>
+  <si>
+    <t>Hint List</t>
+  </si>
+  <si>
+    <t>Invalid Hint Count</t>
+  </si>
+  <si>
+    <t>Invalid Hint List</t>
+  </si>
+  <si>
+    <t>plan_hint</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>t1, t2</t>
+  </si>
+  <si>
     <t>complex_procedure</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>SALARY_HISTORY, NOTIFICATIONS, EMPLOYEE, EMPLOYEES, DEPARTMENT, DEPARTMENT_BUDGETS, JOBS</t>
+    <t>employees, jobs, salary_history, department_budgets, notifications, EMPLOYEE, DEPARTMENT</t>
   </si>
   <si>
     <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["-- Update employee salary","UPDATE employees","INSERT INTO salary_history (","-- Update department budget if necessary","UPDATE department_budgets","INSERT INTO notifications ("],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"complex_procedure","sourceLine":21}]</t>
@@ -104,13 +122,13 @@
     <t>b</t>
   </si>
   <si>
-    <t>PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE</t>
+    <t>PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE112</t>
   </si>
   <si>
     <t>facc_fiact_tmp</t>
   </si>
   <si>
-    <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["delete from facc_fiact_tmp t where t.workdate = i_date;"],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE","sourceLine":5}]</t>
+    <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["delete from facc_fiact_tmp t where t.workdate = i_date;"],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE112","sourceLine":5}]</t>
   </si>
   <si>
     <t>PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE111</t>
@@ -119,10 +137,19 @@
     <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["delete from facc_fiact_tmp t where t.workdate = i_date;"],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE111","sourceLine":5}]</t>
   </si>
   <si>
+    <t>PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE113</t>
+  </si>
+  <si>
+    <t>facc_fiact_tmp, t1, t2</t>
+  </si>
+  <si>
+    <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["delete from facc_fiact_tmp t where t.workdate = i_date;"],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"PKG_FACC_DATAPROC.PROC_UPDATE_BALANCE113","sourceLine":5}]</t>
+  </si>
+  <si>
     <t>custom_functions_procedure</t>
   </si>
   <si>
-    <t>ORDERS, ORDER_ITEMS, NOTIFICATIONS, ERROR_LOG, CUSTOMER, CUSTOMERS, SHOPPING_CART, DUAL, CART</t>
+    <t>customers, shopping_cart, DUAL, orders, order_items, notifications, error_log, CUSTOMER, CART</t>
   </si>
   <si>
     <t>[]</t>
@@ -134,7 +161,7 @@
     <t>c</t>
   </si>
   <si>
-    <t>OAM_APP, OAMU_APP, OAM_BATCH_ALT_TMP</t>
+    <t>(select, DYNAMIC_TABLE, oamu_app, oam_batch_alt_tmp, OAM_APP</t>
   </si>
   <si>
     <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["UPDATE oam_app t SET t.app_state = 10 WHERE t.app_no = i_app_no;","UPDATE oamu_app t SET t.app_state = 10 WHERE t.app_no = i_app_no;","DELETE FROM oam_batch_alt_tmp t WHERE t.app_no = i_app_no;"],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"c","sourceLine":386},{"name":"IMPLICIT_SUBTRANS_2","type":"IMPLICIT","dmlStatements":["UPDATE oam_app t SET t.app_state = 10 WHERE t.app_no = i_app_no;","UPDATE oamu_app t SET t.app_state = 10 WHERE t.app_no = i_app_no;"],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"c","sourceLine":437}]</t>
@@ -155,6 +182,9 @@
     <t>mid_yjqs_detail</t>
   </si>
   <si>
+    <t>bad_hint</t>
+  </si>
+  <si>
     <t>d</t>
   </si>
   <si>
@@ -164,25 +194,25 @@
     <t>nested_loops_procedure</t>
   </si>
   <si>
-    <t>PERFORMANCE_ANALYSIS_LOG, DIC_SUB, LARGE_SALE_ANALYSIS, EMPLOYEE_PERFORMANCE, DEPARTMENT_PERFORMANCE, OVERALL_PERFORMANCE, PERFORMANCE_ALERTS, ERROR_LOG, DEPARTMENT, SALES, PREVIOUS</t>
+    <t>sales, performance_analysis_log, dic_sub, large_sale_analysis, employee_performance, department_performance, overall_performance, performance_alerts, error_log, DEPARTMENT, DEPARTMENTS, EMPLOYEES, PREVIOUS</t>
   </si>
   <si>
     <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["INSERT INTO performance_analysis_log ("],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"nested_loops_procedure","sourceLine":82},{"name":"IMPLICIT_SUBTRANS_2","type":"IMPLICIT","dmlStatements":["insert into dic_sub (id) values('a');","insert into dic_sub (id) values('a');","INSERT INTO large_sale_analysis (","insert into dic_sub (id) values('a');","insert into dic_sub (id) values('a');","INSERT INTO large_sale_analysis (","-- Update department totals","INSERT INTO employee_performance (","INSERT INTO department_performance (","INSERT INTO overall_performance (","INSERT INTO performance_alerts (","INSERT INTO error_log ("],"savepointOperations":[],"nestingLevel":1,"sourceProcedure":"nested_loops_procedure","sourceLine":115}]</t>
   </si>
   <si>
-    <t>ADD_MONTHS:3, C_EMPLOYEES:2(in loop), C_SALES:7(in loop), RECORD:2</t>
+    <t>C_EMPLOYEES:2(in loop), C_SALES:7(in loop), RECORD:2</t>
   </si>
   <si>
     <t>nested_procedure_calls</t>
   </si>
   <si>
-    <t>COMMISSION_LOG, DEDUCTION_LOG, PAYSLIPS, PAYMENT_HISTORY, ERROR_LOG, DEPARTMENT_PAYROLLS, COMPANY_PAYROLLS, PAYROLL_REPORTS, EMPLOYEE, DEPARTMENT, COMPANY, DEPARTMENTS, EMPLOYEES, SALES, SALE_DATE, EMPLOYEE_BENEFITS, DUAL</t>
+    <t>departments, employees, sales, sale_date, commission_log, employee_benefits, deduction_log, DUAL, payslips, payment_history, error_log, department_payrolls, company_payrolls, payroll_reports, EMPLOYEE, DEPARTMENT, COMPANY</t>
   </si>
   <si>
     <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["INSERT INTO payslips (","-- Update employee payment history","INSERT INTO payment_history (","-- Update department totals","INSERT INTO error_log ("],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"nested_procedure_calls","sourceLine":183},{"name":"IMPLICIT_SUBTRANS_2","type":"IMPLICIT","dmlStatements":["INSERT INTO department_payrolls (","INSERT INTO error_log ("],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"nested_procedure_calls","sourceLine":294},{"name":"IMPLICIT_SUBTRANS_3","type":"IMPLICIT","dmlStatements":["INSERT INTO company_payrolls (","INSERT INTO error_log ("],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"nested_procedure_calls","sourceLine":397}]</t>
   </si>
   <si>
-    <t>CALCULATE_COMMISSION:1, CALCULATE_DEDUCTIONS:1, LAST_DAY:1, PROCESS_DEPARTMENT_PAYROLL:1(in loop), PROCESS_EMPLOYEE_PAYROLL:1(in loop)</t>
+    <t>CALCULATE_COMMISSION:1, CALCULATE_DEDUCTIONS:1, PROCESS_DEPARTMENT_PAYROLL:1(in loop), PROCESS_EMPLOYEE_PAYROLL:1(in loop)</t>
   </si>
   <si>
     <t>cte_query</t>
@@ -191,19 +221,16 @@
     <t>simple_procedure</t>
   </si>
   <si>
-    <t>EMPLOYEES</t>
+    <t>employees</t>
   </si>
   <si>
     <t>delete_test2</t>
   </si>
   <si>
-    <t>MID_YJQS_DETAIL</t>
-  </si>
-  <si>
     <t>AAATEST2</t>
   </si>
   <si>
-    <t>EMPTY_CLOB:1, MAP_OBJECT:1, META.P_MT_STD_COVER_LOG.R_COVER_LOG:1, NUMTABLETYPE:1, PKG_HTTP_MNG.PRC_ADD_RECV_INST:1, PKG_HTTP_MNG.PRC_SEND_HTTP_XML_TO_EB:1, PKG_HTTP_MNG.PRC_SPLIT_HTTP_XML_FROM_EB:1, PKG_HTTP_MNG.PRC_UPDATE_HTTP_SEND_XML:1, V_XML.GETCLOBVAL:2, XMLTYPE:1</t>
+    <t>MAP_OBJECT:1, META.P_MT_STD_COVER_LOG.R_COVER_LOG:1, NUMTABLETYPE:1, PKG_HTTP_MNG.PRC_ADD_RECV_INST:1, PKG_HTTP_MNG.PRC_SEND_HTTP_XML_TO_EB:1, PKG_HTTP_MNG.PRC_SPLIT_HTTP_XML_FROM_EB:1, PKG_HTTP_MNG.PRC_UPDATE_HTTP_SEND_XML:1, V_XML.GETCLOBVAL:2, XMLTYPE:1</t>
   </si>
   <si>
     <t>._AAATEST2</t>
@@ -212,19 +239,16 @@
     <t>simple_query</t>
   </si>
   <si>
-    <t>employees</t>
-  </si>
-  <si>
     <t>AAATEST1</t>
   </si>
   <si>
-    <t>MID_YJQS_DETAIL, PAR_CLR_ACNT_INFO, PAR_ACCOUNT_CUSSENT, P_SQL2</t>
+    <t>PAR_ACCOUNT_CUSSENT, par_clr_acnt_info, mid_yjqs_detail, P_SQL2</t>
   </si>
   <si>
     <t>[{"name":"IMPLICIT_SUBTRANS_1","type":"IMPLICIT","dmlStatements":["insert into par_clr_acnt_info"],"savepointOperations":[],"nestingLevel":0,"sourceProcedure":"AAATEST1","sourceLine":305}]</t>
   </si>
   <si>
-    <t>FNC_COM_ACCOUNT_CHECK:1, FNC_COM_IF_FUND:1, INSTR:2(in loop), PKG_HTTP_MNG.PRC_ADD_RECV_INST:1, PKG_HTTP_MNG.PRC_SEND_HTTP_XML_TO_EB:1, PKG_HTTP_MNG.PRC_SPLIT_HTTP_XML_FROM_EB:1, PKG_HTTP_MNG.PRC_UPDATE_HTTP_SEND_XML:1, V_COLCOST:23(in loop), V_XML.GETCLOBVAL:1, XMLTYPE:1</t>
+    <t>FNC_COM_ACCOUNT_CHECK:1, FNC_COM_IF_FUND:1, PKG_HTTP_MNG.PRC_ADD_RECV_INST:1, PKG_HTTP_MNG.PRC_SEND_HTTP_XML_TO_EB:1, PKG_HTTP_MNG.PRC_SPLIT_HTTP_XML_FROM_EB:1, PKG_HTTP_MNG.PRC_UPDATE_HTTP_SEND_XML:1, V_COLCOST:23(in loop), V_XML.GETCLOBVAL:1, XMLTYPE:1</t>
   </si>
   <si>
     <t>._AAATEST1</t>
@@ -358,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:Z35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.76953125" customWidth="true" bestFit="true"/>
@@ -375,7 +399,7 @@
     <col min="12" max="12" width="26.80078125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="16.2109375" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="12.578125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="235.9921875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="209.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="15.46875" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="17.85546875" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="21.48046875" customWidth="true" bestFit="true"/>
@@ -383,6 +407,10 @@
     <col min="20" max="20" width="255.0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="21.03515625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="11.32421875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="9.13671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.3125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,19 +480,31 @@
       <c r="V1" t="s" s="1">
         <v>21</v>
       </c>
+      <c r="W1" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s" s="1">
+        <v>25</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>115.0</v>
+        <v>3.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>140.0</v>
+        <v>53.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>0.0</v>
@@ -476,63 +516,75 @@
         <v>0.0</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K2" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="O2" t="s" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P2" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q2" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S2" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T2" t="s" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U2" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V2" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z2" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>12.0</v>
+        <v>115.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>140.0</v>
+        <v>160.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>0.0</v>
@@ -544,63 +596,75 @@
         <v>0.0</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="O3" t="s" s="0">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P3" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q3" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T3" t="s" s="0">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="U3" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V3" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z3" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>27.0</v>
+        <v>12.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>0.0</v>
+        <v>140.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>0.0</v>
@@ -612,34 +676,34 @@
         <v>0.0</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="P4" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n" s="0">
         <v>0.0</v>
@@ -648,27 +712,39 @@
         <v>0.0</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U4" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z4" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>0.0</v>
@@ -680,57 +756,69 @@
         <v>0.0</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P5" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="U5" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z5" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>28.0</v>
@@ -748,19 +836,19 @@
         <v>0.0</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n" s="0">
         <v>0.0</v>
@@ -769,13 +857,13 @@
         <v>1.0</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="P6" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R6" t="n" s="0">
         <v>1.0</v>
@@ -784,13 +872,25 @@
         <v>0.0</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U6" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z6" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -798,13 +898,13 @@
         <v>35</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>292.0</v>
+        <v>28.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>270.0</v>
+        <v>45.0</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>0.0</v>
@@ -816,63 +916,75 @@
         <v>0.0</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I7" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N7" t="n" s="0">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="O7" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P7" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q7" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R7" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S7" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T7" t="s" s="0">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U7" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="V7" t="s" s="0">
-        <v>38</v>
+        <v>27</v>
+      </c>
+      <c r="W7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z7" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>463.0</v>
+        <v>36.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>463.0</v>
+        <v>121.0</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>0.0</v>
@@ -884,63 +996,75 @@
         <v>0.0</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M8" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N8" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="O8" t="s" s="0">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P8" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q8" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R8" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="S8" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T8" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="U8" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="V8" t="s" s="0">
-        <v>42</v>
+        <v>27</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z8" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>116.0</v>
+        <v>292.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>140.0</v>
+        <v>300.0</v>
       </c>
       <c r="E9" t="n" s="0">
         <v>0.0</v>
@@ -952,63 +1076,75 @@
         <v>0.0</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I9" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L9" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N9" t="n" s="0">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="O9" t="s" s="0">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="P9" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q9" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S9" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T9" t="s" s="0">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U9" t="n" s="0">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="V9" t="s" s="0">
-        <v>23</v>
+        <v>47</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z9" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>3.0</v>
+        <v>463.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>10.0</v>
+        <v>508.0</v>
       </c>
       <c r="E10" t="n" s="0">
         <v>0.0</v>
@@ -1020,63 +1156,75 @@
         <v>0.0</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I10" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L10" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N10" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="O10" t="s" s="0">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P10" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q10" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S10" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T10" t="s" s="0">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n" s="0">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="V10" t="s" s="0">
-        <v>23</v>
+        <v>51</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X10" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z10" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>143.0</v>
+        <v>116.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>168.0</v>
+        <v>160.0</v>
       </c>
       <c r="E11" t="n" s="0">
         <v>0.0</v>
@@ -1088,185 +1236,221 @@
         <v>0.0</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I11" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L11" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M11" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N11" t="n" s="0">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="O11" t="s" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P11" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q11" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R11" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S11" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T11" t="s" s="0">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="U11" t="n" s="0">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="V11" t="s" s="0">
-        <v>48</v>
+        <v>27</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X11" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z11" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>363.0</v>
+        <v>3.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>315.0</v>
+        <v>10.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K12" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L12" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N12" t="n" s="0">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="O12" t="s" s="0">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P12" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q12" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R12" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="S12" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T12" t="s" s="0">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="U12" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="V12" t="s" s="0">
-        <v>52</v>
+        <v>27</v>
+      </c>
+      <c r="W12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X12" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z12" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>525.0</v>
+        <v>3.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>420.0</v>
+        <v>53.0</v>
       </c>
       <c r="E13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="F13" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="I13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="J13" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="K13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="L13" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="M13" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="N13" t="n" s="0">
-        <v>17.0</v>
-      </c>
       <c r="O13" t="s" s="0">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="P13" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q13" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="S13" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T13" t="s" s="0">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="U13" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="V13" t="s" s="0">
-        <v>56</v>
+        <v>27</v>
+      </c>
+      <c r="W13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z13" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -1274,13 +1458,13 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>59.0</v>
+        <v>143.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>0.0</v>
+        <v>168.0</v>
       </c>
       <c r="E14" t="n" s="0">
         <v>0.0</v>
@@ -1292,19 +1476,19 @@
         <v>0.0</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I14" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L14" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M14" t="n" s="0">
         <v>0.0</v>
@@ -1313,13 +1497,13 @@
         <v>0.0</v>
       </c>
       <c r="O14" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P14" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q14" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R14" t="n" s="0">
         <v>0.0</v>
@@ -1328,163 +1512,199 @@
         <v>0.0</v>
       </c>
       <c r="T14" t="s" s="0">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="U14" t="n" s="0">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="V14" t="s" s="0">
-        <v>23</v>
+        <v>58</v>
+      </c>
+      <c r="W14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X14" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z14" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>4.0</v>
+        <v>363.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>30.0</v>
+        <v>375.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G15" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I15" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L15" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M15" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N15" t="n" s="0">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="O15" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P15" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q15" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R15" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S15" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T15" t="s" s="0">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="U15" t="n" s="0">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="V15" t="s" s="0">
-        <v>23</v>
+        <v>62</v>
+      </c>
+      <c r="W15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X15" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z15" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>8.0</v>
+        <v>525.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>45.0</v>
+        <v>460.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L16" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N16" t="n" s="0">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="O16" t="s" s="0">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P16" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q16" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R16" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="S16" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T16" t="s" s="0">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="U16" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="V16" t="s" s="0">
-        <v>23</v>
+        <v>66</v>
+      </c>
+      <c r="W16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X16" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z16" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>80.0</v>
+        <v>59.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="E17" t="n" s="0">
         <v>0.0</v>
@@ -1496,19 +1716,19 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I17" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J17" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L17" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M17" t="n" s="0">
         <v>0.0</v>
@@ -1517,13 +1737,13 @@
         <v>0.0</v>
       </c>
       <c r="O17" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P17" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q17" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R17" t="n" s="0">
         <v>0.0</v>
@@ -1532,27 +1752,39 @@
         <v>0.0</v>
       </c>
       <c r="T17" t="s" s="0">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="U17" t="n" s="0">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="V17" t="s" s="0">
-        <v>63</v>
+        <v>27</v>
+      </c>
+      <c r="W17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z17" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="E18" t="n" s="0">
         <v>0.0</v>
@@ -1564,34 +1796,34 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I18" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J18" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L18" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M18" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N18" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O18" t="s" s="0">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="P18" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q18" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R18" t="n" s="0">
         <v>0.0</v>
@@ -1600,27 +1832,39 @@
         <v>0.0</v>
       </c>
       <c r="T18" t="s" s="0">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="U18" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V18" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X18" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z18" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>15.0</v>
+        <v>50.0</v>
       </c>
       <c r="E19" t="n" s="0">
         <v>0.0</v>
@@ -1632,19 +1876,19 @@
         <v>0.0</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I19" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J19" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L19" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M19" t="n" s="0">
         <v>0.0</v>
@@ -1653,13 +1897,13 @@
         <v>1.0</v>
       </c>
       <c r="O19" t="s" s="0">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="P19" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q19" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R19" t="n" s="0">
         <v>0.0</v>
@@ -1668,92 +1912,116 @@
         <v>0.0</v>
       </c>
       <c r="T19" t="s" s="0">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="U19" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V19" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X19" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z19" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>352.0</v>
+        <v>80.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>335.0</v>
+        <v>30.0</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I20" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J20" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L20" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M20" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N20" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="O20" t="s" s="0">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="P20" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q20" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R20" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="S20" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T20" t="s" s="0">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="U20" t="n" s="0">
-        <v>33.0</v>
+        <v>10.0</v>
       </c>
       <c r="V20" t="s" s="0">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="W20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X20" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z20" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="D21" t="n" s="0">
         <v>0.0</v>
@@ -1768,19 +2036,19 @@
         <v>0.0</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I21" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M21" t="n" s="0">
         <v>0.0</v>
@@ -1789,13 +2057,13 @@
         <v>0.0</v>
       </c>
       <c r="O21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P21" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R21" t="n" s="0">
         <v>0.0</v>
@@ -1804,27 +2072,39 @@
         <v>0.0</v>
       </c>
       <c r="T21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U21" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V21" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X21" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z21" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="E22" t="n" s="0">
         <v>0.0</v>
@@ -1836,19 +2116,19 @@
         <v>0.0</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I22" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J22" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L22" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M22" t="n" s="0">
         <v>0.0</v>
@@ -1857,13 +2137,13 @@
         <v>1.0</v>
       </c>
       <c r="O22" t="s" s="0">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P22" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q22" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R22" t="n" s="0">
         <v>0.0</v>
@@ -1872,57 +2152,69 @@
         <v>0.0</v>
       </c>
       <c r="T22" t="s" s="0">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="U22" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V22" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X22" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z22" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>75</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>8.0</v>
+        <v>352.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>50.0</v>
+        <v>360.0</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I23" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J23" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L23" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M23" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N23" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="O23" t="s" s="0">
         <v>76</v>
@@ -1931,36 +2223,48 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R23" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S23" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="T23" t="s" s="0">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="U23" t="n" s="0">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="V23" t="s" s="0">
-        <v>23</v>
+        <v>78</v>
+      </c>
+      <c r="W23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X23" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z23" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="E24" t="n" s="0">
         <v>0.0</v>
@@ -1972,34 +2276,34 @@
         <v>0.0</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I24" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J24" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L24" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M24" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="N24" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O24" t="s" s="0">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="P24" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q24" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R24" t="n" s="0">
         <v>0.0</v>
@@ -2008,27 +2312,39 @@
         <v>0.0</v>
       </c>
       <c r="T24" t="s" s="0">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="U24" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V24" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X24" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z24" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="E25" t="n" s="0">
         <v>0.0</v>
@@ -2040,19 +2356,19 @@
         <v>0.0</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I25" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J25" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K25" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L25" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M25" t="n" s="0">
         <v>0.0</v>
@@ -2061,13 +2377,13 @@
         <v>1.0</v>
       </c>
       <c r="O25" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P25" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q25" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R25" t="n" s="0">
         <v>0.0</v>
@@ -2076,24 +2392,36 @@
         <v>0.0</v>
       </c>
       <c r="T25" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U25" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V25" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X25" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z25" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
       <c r="D26" t="n" s="0">
         <v>50.0</v>
@@ -2108,19 +2436,19 @@
         <v>0.0</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I26" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J26" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K26" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L26" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M26" t="n" s="0">
         <v>0.0</v>
@@ -2129,13 +2457,13 @@
         <v>1.0</v>
       </c>
       <c r="O26" t="s" s="0">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P26" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q26" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R26" t="n" s="0">
         <v>0.0</v>
@@ -2144,24 +2472,36 @@
         <v>0.0</v>
       </c>
       <c r="T26" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U26" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V26" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X26" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z26" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="D27" t="n" s="0">
         <v>50.0</v>
@@ -2176,19 +2516,19 @@
         <v>0.0</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I27" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J27" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K27" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L27" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M27" t="n" s="0">
         <v>0.0</v>
@@ -2197,13 +2537,13 @@
         <v>1.0</v>
       </c>
       <c r="O27" t="s" s="0">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P27" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q27" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R27" t="n" s="0">
         <v>0.0</v>
@@ -2212,24 +2552,36 @@
         <v>0.0</v>
       </c>
       <c r="T27" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U27" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V27" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X27" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z27" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="D28" t="n" s="0">
         <v>50.0</v>
@@ -2244,19 +2596,19 @@
         <v>0.0</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I28" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J28" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L28" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M28" t="n" s="0">
         <v>0.0</v>
@@ -2265,13 +2617,13 @@
         <v>1.0</v>
       </c>
       <c r="O28" t="s" s="0">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P28" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q28" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R28" t="n" s="0">
         <v>0.0</v>
@@ -2280,24 +2632,36 @@
         <v>0.0</v>
       </c>
       <c r="T28" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U28" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V28" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X28" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z28" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="D29" t="n" s="0">
         <v>50.0</v>
@@ -2312,19 +2676,19 @@
         <v>0.0</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I29" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J29" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L29" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M29" t="n" s="0">
         <v>0.0</v>
@@ -2333,13 +2697,13 @@
         <v>1.0</v>
       </c>
       <c r="O29" t="s" s="0">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P29" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q29" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R29" t="n" s="0">
         <v>0.0</v>
@@ -2348,24 +2712,36 @@
         <v>0.0</v>
       </c>
       <c r="T29" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U29" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V29" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X29" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z29" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="D30" t="n" s="0">
         <v>50.0</v>
@@ -2380,19 +2756,19 @@
         <v>0.0</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I30" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J30" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K30" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L30" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M30" t="n" s="0">
         <v>0.0</v>
@@ -2401,13 +2777,13 @@
         <v>1.0</v>
       </c>
       <c r="O30" t="s" s="0">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P30" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q30" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R30" t="n" s="0">
         <v>0.0</v>
@@ -2416,27 +2792,39 @@
         <v>0.0</v>
       </c>
       <c r="T30" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U30" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V30" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X30" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z30" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>45.0</v>
+        <v>50.0</v>
       </c>
       <c r="E31" t="n" s="0">
         <v>0.0</v>
@@ -2448,19 +2836,19 @@
         <v>0.0</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I31" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J31" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L31" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M31" t="n" s="0">
         <v>0.0</v>
@@ -2469,13 +2857,13 @@
         <v>1.0</v>
       </c>
       <c r="O31" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P31" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q31" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n" s="0">
         <v>0.0</v>
@@ -2484,27 +2872,39 @@
         <v>0.0</v>
       </c>
       <c r="T31" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U31" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V31" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X31" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z31" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>45.0</v>
+        <v>50.0</v>
       </c>
       <c r="E32" t="n" s="0">
         <v>0.0</v>
@@ -2516,19 +2916,19 @@
         <v>0.0</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I32" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="J32" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K32" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="L32" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M32" t="n" s="0">
         <v>0.0</v>
@@ -2537,13 +2937,13 @@
         <v>1.0</v>
       </c>
       <c r="O32" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P32" t="b" s="0">
         <v>0</v>
       </c>
       <c r="Q32" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R32" t="n" s="0">
         <v>0.0</v>
@@ -2552,13 +2952,265 @@
         <v>0.0</v>
       </c>
       <c r="T32" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U32" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="V32" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="W32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X32" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z32" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D33" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="E33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L33" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N33" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O33" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="P33" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="R33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="S33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="T33" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="U33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V33" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="W33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X33" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z33" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="n" s="0">
+        <v>45.0</v>
+      </c>
+      <c r="E34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L34" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N34" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O34" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="P34" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="R34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="S34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="T34" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="U34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V34" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="W34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X34" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z34" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D35" t="n" s="0">
+        <v>45.0</v>
+      </c>
+      <c r="E35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L35" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N35" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O35" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="P35" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="R35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="S35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="T35" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="U35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V35" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="W35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X35" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="Y35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Z35" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
